--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,6 +1721,1048 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122529022</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514808</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6366024</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122528652</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>514741</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6365941</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122528093</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>514655</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365907</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122529365</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57395</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>514869</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6365937</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122528403</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>514629</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6365909</v>
+      </c>
+      <c r="S15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122529030</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100477</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>514828</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6366034</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122529196</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105317</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>514862</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6366025</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122528254</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>514655</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6365913</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122529245</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Aspödammen, Aspödammen, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>514856</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6366016</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529022</v>
+        <v>122529365</v>
       </c>
       <c r="B11" t="n">
-        <v>98211</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,35 +1736,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1773,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514808</v>
+        <v>514869</v>
       </c>
       <c r="R11" t="n">
-        <v>6366024</v>
+        <v>6365937</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1808,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,12 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,14 +1829,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122528652</v>
+        <v>122528403</v>
       </c>
       <c r="B12" t="n">
         <v>98211</v>
@@ -1880,17 +1866,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1899,13 +1875,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514741</v>
+        <v>514629</v>
       </c>
       <c r="R12" t="n">
-        <v>6365941</v>
+        <v>6365909</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1934,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122528093</v>
+        <v>122529030</v>
       </c>
       <c r="B13" t="n">
-        <v>98211</v>
+        <v>100477</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,27 +1959,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2015,13 +1987,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514655</v>
+        <v>514828</v>
       </c>
       <c r="R13" t="n">
-        <v>6365907</v>
+        <v>6366034</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,17 +2052,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529365</v>
+        <v>122529196</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>105317</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,26 +2071,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2127,13 +2099,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514869</v>
+        <v>514862</v>
       </c>
       <c r="R14" t="n">
-        <v>6365937</v>
+        <v>6366025</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,14 +2164,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122528403</v>
+        <v>122529245</v>
       </c>
       <c r="B15" t="n">
         <v>98211</v>
@@ -2232,19 +2204,24 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aspödammen, Aspödammen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514629</v>
+        <v>514856</v>
       </c>
       <c r="R15" t="n">
-        <v>6365909</v>
+        <v>6366016</v>
       </c>
       <c r="S15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2273,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,7 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122529030</v>
+        <v>122529022</v>
       </c>
       <c r="B16" t="n">
-        <v>100477</v>
+        <v>98211</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,41 +2299,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspödammen, Aspödammen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514828</v>
+        <v>514808</v>
       </c>
       <c r="R16" t="n">
-        <v>6366034</v>
+        <v>6366024</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2385,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2395,7 +2375,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,6 +2389,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2422,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122529196</v>
+        <v>122528254</v>
       </c>
       <c r="B17" t="n">
-        <v>105317</v>
+        <v>98211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,41 +2420,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aspödammen, Aspödammen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514862</v>
+        <v>514655</v>
       </c>
       <c r="R17" t="n">
-        <v>6366025</v>
+        <v>6365913</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2497,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2507,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,6 +2505,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2527,14 +2517,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528254</v>
+        <v>122528652</v>
       </c>
       <c r="B18" t="n">
         <v>98211</v>
@@ -2564,24 +2554,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Aspödammen, Aspödammen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514655</v>
+        <v>514741</v>
       </c>
       <c r="R18" t="n">
-        <v>6365913</v>
+        <v>6365941</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2613,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,6 +2621,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2650,7 +2640,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122529245</v>
+        <v>122528093</v>
       </c>
       <c r="B19" t="n">
         <v>98211</v>
@@ -2680,27 +2670,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aspödammen, Aspödammen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514856</v>
+        <v>514655</v>
       </c>
       <c r="R19" t="n">
-        <v>6366016</v>
+        <v>6365907</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,6 +2737,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529365</v>
+        <v>122529030</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,26 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514869</v>
+        <v>514828</v>
       </c>
       <c r="R11" t="n">
-        <v>6365937</v>
+        <v>6366034</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,17 +1834,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122528403</v>
+        <v>122529365</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,25 +1853,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1875,13 +1886,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514629</v>
+        <v>514869</v>
       </c>
       <c r="R12" t="n">
-        <v>6365909</v>
+        <v>6365937</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529030</v>
+        <v>122529196</v>
       </c>
       <c r="B13" t="n">
-        <v>100477</v>
+        <v>105330</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,22 +1974,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1987,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514828</v>
+        <v>514862</v>
       </c>
       <c r="R13" t="n">
-        <v>6366034</v>
+        <v>6366025</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2022,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529196</v>
+        <v>122528403</v>
       </c>
       <c r="B14" t="n">
-        <v>105317</v>
+        <v>98224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,26 +2087,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2099,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514862</v>
+        <v>514629</v>
       </c>
       <c r="R14" t="n">
-        <v>6366025</v>
+        <v>6365909</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,17 +2184,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122529245</v>
+        <v>122528093</v>
       </c>
       <c r="B15" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,6 +2209,11 @@
       <c r="E15" t="n">
         <v>220787</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2201,27 +2226,26 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aspödammen, Aspödammen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514856</v>
+        <v>514655</v>
       </c>
       <c r="R15" t="n">
-        <v>6366016</v>
+        <v>6365907</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,6 +2293,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2287,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122529022</v>
+        <v>122528254</v>
       </c>
       <c r="B16" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,6 +2330,11 @@
       <c r="E16" t="n">
         <v>220787</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2317,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2330,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514808</v>
+        <v>514655</v>
       </c>
       <c r="R16" t="n">
-        <v>6366024</v>
+        <v>6365913</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2365,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,12 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,17 +2426,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122528254</v>
+        <v>122529022</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,6 +2451,11 @@
       <c r="E17" t="n">
         <v>220787</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2438,7 +2468,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2451,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514655</v>
+        <v>514808</v>
       </c>
       <c r="R17" t="n">
-        <v>6365913</v>
+        <v>6366024</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2486,7 +2516,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2526,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,17 +2552,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528652</v>
+        <v>122529245</v>
       </c>
       <c r="B18" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,6 +2577,11 @@
       <c r="E18" t="n">
         <v>220787</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2554,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2567,13 +2607,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514741</v>
+        <v>514856</v>
       </c>
       <c r="R18" t="n">
-        <v>6365941</v>
+        <v>6366016</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2602,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122528093</v>
+        <v>122528652</v>
       </c>
       <c r="B19" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,6 +2698,11 @@
       <c r="E19" t="n">
         <v>220787</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2670,7 +2715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2683,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514655</v>
+        <v>514741</v>
       </c>
       <c r="R19" t="n">
-        <v>6365907</v>
+        <v>6365941</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2718,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529030</v>
+        <v>122528403</v>
       </c>
       <c r="B11" t="n">
-        <v>100490</v>
+        <v>98237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1768,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514828</v>
+        <v>514629</v>
       </c>
       <c r="R11" t="n">
-        <v>6366034</v>
+        <v>6365909</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,17 +1833,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122529365</v>
+        <v>122529196</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>105343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,31 +1852,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1886,13 +1885,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514869</v>
+        <v>514862</v>
       </c>
       <c r="R12" t="n">
-        <v>6365937</v>
+        <v>6366025</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,17 +1950,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529196</v>
+        <v>122529030</v>
       </c>
       <c r="B13" t="n">
-        <v>105330</v>
+        <v>100503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,27 +1973,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2003,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514862</v>
+        <v>514828</v>
       </c>
       <c r="R13" t="n">
-        <v>6366025</v>
+        <v>6366034</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122528403</v>
+        <v>122529365</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,30 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514629</v>
+        <v>514869</v>
       </c>
       <c r="R14" t="n">
-        <v>6365909</v>
+        <v>6365937</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,7 +2194,7 @@
         <v>122528093</v>
       </c>
       <c r="B15" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>122528254</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122529022</v>
+        <v>122528652</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514808</v>
+        <v>514741</v>
       </c>
       <c r="R17" t="n">
-        <v>6366024</v>
+        <v>6365941</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2526,12 +2526,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,17 +2547,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122529245</v>
+        <v>122529022</v>
       </c>
       <c r="B18" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2607,13 +2602,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514856</v>
+        <v>514808</v>
       </c>
       <c r="R18" t="n">
-        <v>6366016</v>
+        <v>6366024</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2647,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122528652</v>
+        <v>122529245</v>
       </c>
       <c r="B19" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514741</v>
+        <v>514856</v>
       </c>
       <c r="R19" t="n">
-        <v>6365941</v>
+        <v>6366016</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122528403</v>
+        <v>122529196</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>105343</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,30 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514629</v>
+        <v>514862</v>
       </c>
       <c r="R11" t="n">
-        <v>6365909</v>
+        <v>6366025</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,17 +1834,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122529196</v>
+        <v>122528403</v>
       </c>
       <c r="B12" t="n">
-        <v>105343</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,31 +1853,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514862</v>
+        <v>514629</v>
       </c>
       <c r="R12" t="n">
-        <v>6366025</v>
+        <v>6365909</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122528093</v>
+        <v>122529022</v>
       </c>
       <c r="B15" t="n">
         <v>98237</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514655</v>
+        <v>514808</v>
       </c>
       <c r="R15" t="n">
-        <v>6365907</v>
+        <v>6366024</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,7 +2284,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,7 +2310,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2433,7 +2438,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122528652</v>
+        <v>122529245</v>
       </c>
       <c r="B17" t="n">
         <v>98237</v>
@@ -2468,7 +2473,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2481,13 +2486,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514741</v>
+        <v>514856</v>
       </c>
       <c r="R17" t="n">
-        <v>6365941</v>
+        <v>6366016</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2516,7 +2521,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2526,7 +2531,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,7 +2559,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122529022</v>
+        <v>122528093</v>
       </c>
       <c r="B18" t="n">
         <v>98237</v>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2602,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514808</v>
+        <v>514655</v>
       </c>
       <c r="R18" t="n">
-        <v>6366024</v>
+        <v>6365907</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2637,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,12 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,14 +2673,14 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122529245</v>
+        <v>122528652</v>
       </c>
       <c r="B19" t="n">
         <v>98237</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514856</v>
+        <v>514741</v>
       </c>
       <c r="R19" t="n">
-        <v>6366016</v>
+        <v>6365941</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>122529196</v>
       </c>
       <c r="B11" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122528403</v>
+        <v>122529365</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,30 +1853,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,13 +1886,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514629</v>
+        <v>514869</v>
       </c>
       <c r="R12" t="n">
-        <v>6365909</v>
+        <v>6365937</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529030</v>
+        <v>122528403</v>
       </c>
       <c r="B13" t="n">
-        <v>100503</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,31 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514828</v>
+        <v>514629</v>
       </c>
       <c r="R13" t="n">
-        <v>6366034</v>
+        <v>6365909</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529365</v>
+        <v>122529030</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,31 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514869</v>
+        <v>514828</v>
       </c>
       <c r="R14" t="n">
-        <v>6365937</v>
+        <v>6366034</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122529022</v>
+        <v>122529245</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514808</v>
+        <v>514856</v>
       </c>
       <c r="R15" t="n">
-        <v>6366024</v>
+        <v>6366016</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,12 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,17 +2305,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122528254</v>
+        <v>122528093</v>
       </c>
       <c r="B16" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2368,7 +2363,7 @@
         <v>514655</v>
       </c>
       <c r="R16" t="n">
-        <v>6365913</v>
+        <v>6365907</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2400,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122529245</v>
+        <v>122529022</v>
       </c>
       <c r="B17" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,7 +2468,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2486,13 +2481,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514856</v>
+        <v>514808</v>
       </c>
       <c r="R17" t="n">
-        <v>6366016</v>
+        <v>6366024</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2521,7 +2516,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,7 +2526,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528093</v>
+        <v>122528254</v>
       </c>
       <c r="B18" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2610,7 +2610,7 @@
         <v>514655</v>
       </c>
       <c r="R18" t="n">
-        <v>6365907</v>
+        <v>6365913</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,7 +2683,7 @@
         <v>122528652</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529196</v>
+        <v>122529365</v>
       </c>
       <c r="B11" t="n">
-        <v>105346</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514862</v>
+        <v>514869</v>
       </c>
       <c r="R11" t="n">
-        <v>6366025</v>
+        <v>6365937</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122529365</v>
+        <v>122529030</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,31 +1853,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514869</v>
+        <v>514828</v>
       </c>
       <c r="R12" t="n">
-        <v>6365937</v>
+        <v>6366034</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,17 +1951,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122528403</v>
+        <v>122529196</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>105346</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1970,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514629</v>
+        <v>514862</v>
       </c>
       <c r="R13" t="n">
-        <v>6365909</v>
+        <v>6366025</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,17 +2068,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529030</v>
+        <v>122528403</v>
       </c>
       <c r="B14" t="n">
-        <v>100506</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,31 +2087,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514828</v>
+        <v>514629</v>
       </c>
       <c r="R14" t="n">
-        <v>6366034</v>
+        <v>6365909</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122529245</v>
+        <v>122529022</v>
       </c>
       <c r="B15" t="n">
         <v>98240</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514856</v>
+        <v>514808</v>
       </c>
       <c r="R15" t="n">
-        <v>6366016</v>
+        <v>6366024</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,7 +2284,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,7 +2310,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2433,7 +2438,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122529022</v>
+        <v>122529245</v>
       </c>
       <c r="B17" t="n">
         <v>98240</v>
@@ -2468,7 +2473,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2481,13 +2486,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514808</v>
+        <v>514856</v>
       </c>
       <c r="R17" t="n">
-        <v>6366024</v>
+        <v>6366016</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2516,7 +2521,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2526,12 +2531,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,14 +2552,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528254</v>
+        <v>122528652</v>
       </c>
       <c r="B18" t="n">
         <v>98240</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514655</v>
+        <v>514741</v>
       </c>
       <c r="R18" t="n">
-        <v>6365913</v>
+        <v>6365941</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122528652</v>
+        <v>122528254</v>
       </c>
       <c r="B19" t="n">
         <v>98240</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514741</v>
+        <v>514655</v>
       </c>
       <c r="R19" t="n">
-        <v>6365941</v>
+        <v>6365913</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529365</v>
+        <v>122529196</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>105347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514869</v>
+        <v>514862</v>
       </c>
       <c r="R11" t="n">
-        <v>6365937</v>
+        <v>6366025</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>122529030</v>
       </c>
       <c r="B12" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1958,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529196</v>
+        <v>122528403</v>
       </c>
       <c r="B13" t="n">
-        <v>105346</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,31 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2003,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514862</v>
+        <v>514629</v>
       </c>
       <c r="R13" t="n">
-        <v>6366025</v>
+        <v>6365909</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,17 +2067,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122528403</v>
+        <v>122529365</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,30 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514629</v>
+        <v>514869</v>
       </c>
       <c r="R14" t="n">
-        <v>6365909</v>
+        <v>6365937</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122529022</v>
+        <v>122528254</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514808</v>
+        <v>514655</v>
       </c>
       <c r="R15" t="n">
-        <v>6366024</v>
+        <v>6365913</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,12 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,17 +2305,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122528093</v>
+        <v>122529022</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2365,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514655</v>
+        <v>514808</v>
       </c>
       <c r="R16" t="n">
-        <v>6365907</v>
+        <v>6366024</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2400,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2405,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122529245</v>
+        <v>122528652</v>
       </c>
       <c r="B17" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2486,13 +2486,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514856</v>
+        <v>514741</v>
       </c>
       <c r="R17" t="n">
-        <v>6366016</v>
+        <v>6365941</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528652</v>
+        <v>122528093</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514741</v>
+        <v>514655</v>
       </c>
       <c r="R18" t="n">
-        <v>6365941</v>
+        <v>6365907</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122528254</v>
+        <v>122529245</v>
       </c>
       <c r="B19" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514655</v>
+        <v>514856</v>
       </c>
       <c r="R19" t="n">
-        <v>6365913</v>
+        <v>6366016</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529196</v>
+        <v>122529365</v>
       </c>
       <c r="B11" t="n">
-        <v>105347</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514862</v>
+        <v>514869</v>
       </c>
       <c r="R11" t="n">
-        <v>6366025</v>
+        <v>6365937</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122529030</v>
+        <v>122528403</v>
       </c>
       <c r="B12" t="n">
-        <v>100507</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,31 +1853,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1886,13 +1885,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514828</v>
+        <v>514629</v>
       </c>
       <c r="R12" t="n">
-        <v>6366034</v>
+        <v>6365909</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,17 +1950,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122528403</v>
+        <v>122529196</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>105350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1969,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514629</v>
+        <v>514862</v>
       </c>
       <c r="R13" t="n">
-        <v>6365909</v>
+        <v>6366025</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529365</v>
+        <v>122529030</v>
       </c>
       <c r="B14" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,31 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514869</v>
+        <v>514828</v>
       </c>
       <c r="R14" t="n">
-        <v>6365937</v>
+        <v>6366034</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122528254</v>
+        <v>122529022</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514655</v>
+        <v>514808</v>
       </c>
       <c r="R15" t="n">
-        <v>6365913</v>
+        <v>6366024</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,7 +2284,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,17 +2310,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122529022</v>
+        <v>122528093</v>
       </c>
       <c r="B16" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2360,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514808</v>
+        <v>514655</v>
       </c>
       <c r="R16" t="n">
-        <v>6366024</v>
+        <v>6365907</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2395,7 +2400,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,12 +2410,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
         <v>122528652</v>
       </c>
       <c r="B17" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528093</v>
+        <v>122528254</v>
       </c>
       <c r="B18" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2610,7 +2610,7 @@
         <v>514655</v>
       </c>
       <c r="R18" t="n">
-        <v>6365907</v>
+        <v>6365913</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,7 +2683,7 @@
         <v>122529245</v>
       </c>
       <c r="B19" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529365</v>
+        <v>122529196</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>105350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514869</v>
+        <v>514862</v>
       </c>
       <c r="R11" t="n">
-        <v>6365937</v>
+        <v>6366025</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122528403</v>
+        <v>122529365</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,30 +1853,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,13 +1886,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514629</v>
+        <v>514869</v>
       </c>
       <c r="R12" t="n">
-        <v>6365909</v>
+        <v>6365937</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529196</v>
+        <v>122529030</v>
       </c>
       <c r="B13" t="n">
-        <v>105350</v>
+        <v>100510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,27 +1974,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514862</v>
+        <v>514828</v>
       </c>
       <c r="R13" t="n">
-        <v>6366025</v>
+        <v>6366034</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529030</v>
+        <v>122528403</v>
       </c>
       <c r="B14" t="n">
-        <v>100510</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,31 +2087,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514828</v>
+        <v>514629</v>
       </c>
       <c r="R14" t="n">
-        <v>6366034</v>
+        <v>6365909</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122529022</v>
+        <v>122528093</v>
       </c>
       <c r="B15" t="n">
         <v>98244</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514808</v>
+        <v>514655</v>
       </c>
       <c r="R15" t="n">
-        <v>6366024</v>
+        <v>6365907</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,12 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,14 +2305,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122528093</v>
+        <v>122529022</v>
       </c>
       <c r="B16" t="n">
         <v>98244</v>
@@ -2352,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2365,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514655</v>
+        <v>514808</v>
       </c>
       <c r="R16" t="n">
-        <v>6365907</v>
+        <v>6366024</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2400,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2410,7 +2405,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529196</v>
+        <v>122529365</v>
       </c>
       <c r="B11" t="n">
-        <v>105350</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514862</v>
+        <v>514869</v>
       </c>
       <c r="R11" t="n">
-        <v>6366025</v>
+        <v>6365937</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122529365</v>
+        <v>122529030</v>
       </c>
       <c r="B12" t="n">
-        <v>57400</v>
+        <v>100613</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,31 +1853,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514869</v>
+        <v>514828</v>
       </c>
       <c r="R12" t="n">
-        <v>6365937</v>
+        <v>6366034</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,17 +1951,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529030</v>
+        <v>122529196</v>
       </c>
       <c r="B13" t="n">
-        <v>100510</v>
+        <v>105453</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,27 +1974,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514828</v>
+        <v>514862</v>
       </c>
       <c r="R13" t="n">
-        <v>6366034</v>
+        <v>6366025</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,7 +2078,7 @@
         <v>122528403</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>122528093</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122529022</v>
+        <v>122529245</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2360,13 +2360,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514808</v>
+        <v>514856</v>
       </c>
       <c r="R16" t="n">
-        <v>6366024</v>
+        <v>6366016</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,12 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,17 +2426,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122528652</v>
+        <v>122528254</v>
       </c>
       <c r="B17" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,7 +2468,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2486,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514741</v>
+        <v>514655</v>
       </c>
       <c r="R17" t="n">
-        <v>6365941</v>
+        <v>6365913</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2521,7 +2516,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2531,7 +2526,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2559,10 +2554,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528254</v>
+        <v>122528652</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2607,10 +2602,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514655</v>
+        <v>514741</v>
       </c>
       <c r="R18" t="n">
-        <v>6365913</v>
+        <v>6365941</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2647,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,10 +2675,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122529245</v>
+        <v>122529022</v>
       </c>
       <c r="B19" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,7 +2710,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2728,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514856</v>
+        <v>514808</v>
       </c>
       <c r="R19" t="n">
-        <v>6366016</v>
+        <v>6366024</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,7 +2758,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2768,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529365</v>
+        <v>122529030</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>100621</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514869</v>
+        <v>514828</v>
       </c>
       <c r="R11" t="n">
-        <v>6365937</v>
+        <v>6366034</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122529030</v>
+        <v>122528403</v>
       </c>
       <c r="B12" t="n">
-        <v>100613</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,31 +1853,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1886,13 +1885,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514828</v>
+        <v>514629</v>
       </c>
       <c r="R12" t="n">
-        <v>6366034</v>
+        <v>6365909</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,7 +1950,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1961,7 +1960,7 @@
         <v>122529196</v>
       </c>
       <c r="B13" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2075,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122528403</v>
+        <v>122529365</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,30 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514629</v>
+        <v>514869</v>
       </c>
       <c r="R14" t="n">
-        <v>6365909</v>
+        <v>6365937</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122528093</v>
+        <v>122528254</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2242,7 +2242,7 @@
         <v>514655</v>
       </c>
       <c r="R15" t="n">
-        <v>6365907</v>
+        <v>6365913</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122529245</v>
+        <v>122528652</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2360,13 +2360,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514856</v>
+        <v>514741</v>
       </c>
       <c r="R16" t="n">
-        <v>6366016</v>
+        <v>6365941</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122528254</v>
+        <v>122529022</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514655</v>
+        <v>514808</v>
       </c>
       <c r="R17" t="n">
-        <v>6365913</v>
+        <v>6366024</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2526,7 +2526,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,17 +2552,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528652</v>
+        <v>122529245</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2602,13 +2607,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514741</v>
+        <v>514856</v>
       </c>
       <c r="R18" t="n">
-        <v>6365941</v>
+        <v>6366016</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2637,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2675,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122529022</v>
+        <v>122528093</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2710,7 +2715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514808</v>
+        <v>514655</v>
       </c>
       <c r="R19" t="n">
-        <v>6366024</v>
+        <v>6365907</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2758,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2768,12 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529030</v>
+        <v>122529365</v>
       </c>
       <c r="B11" t="n">
-        <v>100621</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514828</v>
+        <v>514869</v>
       </c>
       <c r="R11" t="n">
-        <v>6366034</v>
+        <v>6365937</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529196</v>
+        <v>122529030</v>
       </c>
       <c r="B13" t="n">
-        <v>105461</v>
+        <v>100621</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,27 +1973,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514862</v>
+        <v>514828</v>
       </c>
       <c r="R13" t="n">
-        <v>6366025</v>
+        <v>6366034</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529365</v>
+        <v>122529196</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>105461</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,31 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514869</v>
+        <v>514862</v>
       </c>
       <c r="R14" t="n">
-        <v>6365937</v>
+        <v>6366025</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122528254</v>
+        <v>122528652</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514655</v>
+        <v>514741</v>
       </c>
       <c r="R15" t="n">
-        <v>6365913</v>
+        <v>6365941</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122528652</v>
+        <v>122528254</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514741</v>
+        <v>514655</v>
       </c>
       <c r="R16" t="n">
-        <v>6365941</v>
+        <v>6365913</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2559,7 +2559,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122529245</v>
+        <v>122528093</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514856</v>
+        <v>514655</v>
       </c>
       <c r="R18" t="n">
-        <v>6366016</v>
+        <v>6365907</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122528093</v>
+        <v>122529245</v>
       </c>
       <c r="B19" t="n">
         <v>98355</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514655</v>
+        <v>514856</v>
       </c>
       <c r="R19" t="n">
-        <v>6365907</v>
+        <v>6366016</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1724,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529365</v>
+        <v>122529030</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>100623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,31 +1736,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514869</v>
+        <v>514828</v>
       </c>
       <c r="R11" t="n">
-        <v>6365937</v>
+        <v>6366034</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>122528403</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529030</v>
+        <v>122529196</v>
       </c>
       <c r="B13" t="n">
-        <v>100621</v>
+        <v>105463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,27 +1973,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514828</v>
+        <v>514862</v>
       </c>
       <c r="R13" t="n">
-        <v>6366034</v>
+        <v>6366025</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529196</v>
+        <v>122529365</v>
       </c>
       <c r="B14" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,31 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514862</v>
+        <v>514869</v>
       </c>
       <c r="R14" t="n">
-        <v>6366025</v>
+        <v>6365937</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2194,7 +2194,7 @@
         <v>122528652</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122528254</v>
+        <v>122528093</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2363,7 +2363,7 @@
         <v>514655</v>
       </c>
       <c r="R16" t="n">
-        <v>6365913</v>
+        <v>6365907</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122529022</v>
+        <v>122528254</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514808</v>
+        <v>514655</v>
       </c>
       <c r="R17" t="n">
-        <v>6366024</v>
+        <v>6365913</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2526,12 +2526,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>50tal rosetter i detta område</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,17 +2547,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122528093</v>
+        <v>122529245</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2607,13 +2602,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514655</v>
+        <v>514856</v>
       </c>
       <c r="R18" t="n">
-        <v>6365907</v>
+        <v>6366016</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2642,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2652,7 +2647,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2680,10 +2675,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122529245</v>
+        <v>122529022</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,7 +2710,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2728,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514856</v>
+        <v>514808</v>
       </c>
       <c r="R19" t="n">
-        <v>6366016</v>
+        <v>6366024</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,7 +2758,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2768,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>50tal rosetter i detta område</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 1076-2025 artfynd.xlsx
+++ b/artfynd/A 1076-2025 artfynd.xlsx
@@ -1957,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122529196</v>
+        <v>122529365</v>
       </c>
       <c r="B13" t="n">
-        <v>105463</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,31 +1969,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514862</v>
+        <v>514869</v>
       </c>
       <c r="R13" t="n">
-        <v>6366025</v>
+        <v>6365937</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122529365</v>
+        <v>122529196</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,31 +2086,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514869</v>
+        <v>514862</v>
       </c>
       <c r="R14" t="n">
-        <v>6365937</v>
+        <v>6366025</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Cecilia Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122528652</v>
+        <v>122528093</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514741</v>
+        <v>514655</v>
       </c>
       <c r="R15" t="n">
-        <v>6365941</v>
+        <v>6365907</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122528093</v>
+        <v>122529245</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2360,13 +2360,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514655</v>
+        <v>514856</v>
       </c>
       <c r="R16" t="n">
-        <v>6365907</v>
+        <v>6366016</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,7 +2433,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122528254</v>
+        <v>122528652</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514655</v>
+        <v>514741</v>
       </c>
       <c r="R17" t="n">
-        <v>6365913</v>
+        <v>6365941</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,7 +2554,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122529245</v>
+        <v>122528254</v>
       </c>
       <c r="B18" t="n">
         <v>98357</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514856</v>
+        <v>514655</v>
       </c>
       <c r="R18" t="n">
-        <v>6366016</v>
+        <v>6365913</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
